--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0055.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0055.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Tuyệt! Đảm bảo tụi ta sẽ quay lại vì bất ngờ đó!</t>
+          <t>Tuyệt! Đảm bảo tụi tao sẽ quay lại vì bất ngờ đó!</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Không có gì đâu. Ta chỉ làm điều phải thôi.</t>
+          <t>Không có gì đâu. Tao chỉ làm điều phải thôi.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ta à? Ta ước…</t>
+          <t>Tao à? Tao ước…</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Ôi dào, tụi sáng lấp lánh kia học bay kiểu gì mà lượn như thế nhỉ? Ta không thể mãi làm thế này được... Hay mình nhảy lên cái Gondola đằng kia đi?</t>
+          <t>Ôi dào, tụi sáng lấp lánh kia học bay kiểu gì mà lượn như thế nhỉ? Tao không thể mãi làm thế này được... Hay mình nhảy lên cái Gondola đằng kia đi?</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Thôi được, xét cho cùng nó cũng dẫn chúng ta đến bao nhiêu rương kho báu, lần này ta bỏ qua. Nhưng lần sau gặp lại, chúng phải có lời giải thích thỏa đáng đấy.</t>
+          <t>Thôi được, xét cho cùng nó cũng dẫn chúng ta đến bao nhiêu rương kho báu, lần này tao bỏ qua. Nhưng lần sau gặp lại, chúng phải có lời giải thích thỏa đáng đấy.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Ôi, đầu óc choáng váng quá… Ta nằm đây đã. Cứ… cứ gọi nếu cần ta nhé…</t>
+          <t>Ôi, đầu óc choáng váng quá… Tao nằm đây đã. Cứ… cứ gọi nếu cần tao nhé…</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cậu sợ à? Ta thì không!</t>
+          <t>Cậu sợ à? Tao thì không!</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mỗi nơi đều có những thứ riêng của họ. Ta nghĩ chúng chỉ là bịa đặt để dọa người ta và khuấy động không khí lễ hội thôi!</t>
+          <t>Mỗi nơi đều có những thứ riêng của họ. Tao nghĩ chúng chỉ là bịa đặt để dọa người ta và khuấy động không khí lễ hội thôi!</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nhìn cảnh vật bao la này... lòng ta thật sự bình yên biết bao.</t>
+          <t>Nhìn cảnh vật bao la này... lòng tao thật sự bình yên biết bao.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Đến chơi trò này với ta đi. Ta biết ngươi sẽ không bỏ lỡ bất kỳ manh mối tiềm năng nào đâu.</t>
+          <t>Đến chơi trò này với ta đi. Tao biết mày sẽ không bỏ lỡ bất kỳ manh mối tiềm năng nào đâu.</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Haha, ta thích sự thẳng thắn của cậu! Đúng rồi, chúng nó chẳng khác gì nhau cả, phải không?</t>
+          <t>Haha, tao thích sự thẳng thắn của cậu! Đúng rồi, chúng nó chẳng khác gì nhau cả, phải không?</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -19621,7 +19621,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Giai điệu này gợi lên cảm giác quen thuộc, nhắc ta nhớ về nơi ấy—&lt;ano=Castle of Fisalia&gt;Lâu đài Porto-Veno&lt;/ano&gt;.</t>
+          <t>Giai điệu này gợi lên cảm giác quen thuộc, nhắc ta nhớ về nơi ấy—&lt;ano=Castle of Fisalia&gt;Porto-Veno Castle&lt;/ano&gt;.</t>
         </is>
       </c>
     </row>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Hai loài thực vật chết người này đã được các thế hệ gia tộc Fisalias chăm sóc tỉ mỉ, sinh sôi nảy nở trong khu vườn của Lâu đài Porto-Veno suốt nhiều thế kỷ.</t>
+          <t>Hai loài thực vật chết người này đã được các thế hệ gia tộc Fisalias chăm sóc tỉ mỉ, sinh sôi nảy nở trong khu vườn của Porto-Veno Castle suốt nhiều thế kỷ.</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26838,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Cậu làm da gà ta nổi hết lên rồi.</t>
+          <t>Cậu làm da gà tao nổi hết lên rồi.</t>
         </is>
       </c>
     </row>
@@ -31323,7 +31323,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Ngươi ghét luật lệ của chúng ta, nhưng chúng đã ngấm vào từng thớ thịt ngươi rồi.</t>
+          <t>Mày ghét luật lệ của chúng tao, nhưng chúng đã ngấm vào từng thớ thịt mày rồi.</t>
         </is>
       </c>
     </row>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Bọn Giáo Đoàn lúc nào cũng tò mò, háo hức tìm kiếm sự thật... Ta biết nếu chúng ta hành động liều lĩnh, chỉ chuốc lấy nguy hiểm thôi.</t>
+          <t>Bọn Giáo Đoàn lúc nào cũng tò mò, háo hức tìm kiếm sự thật... Tao biết nếu chúng ta hành động liều lĩnh, chỉ chuốc lấy nguy hiểm thôi.</t>
         </is>
       </c>
     </row>
@@ -32948,7 +32948,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Nhưng... ta nhớ nhà thật sự, nhiều hơn những gì ta có thể diễn tả.</t>
+          <t>Nhưng... tao nhớ nhà thật sự, nhiều hơn những gì tao có thể diễn tả.</t>
         </is>
       </c>
     </row>
